--- a/data/trans_orig/P14B23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2012</t>
+          <t>Población cuya depresión o ansiedad le limita en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14415</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>23684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422796</t>
+          <t>424233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435211</t>
+          <t>435285</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297641</t>
+          <t>298639</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311893</t>
+          <t>312588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727162</t>
+          <t>727981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745238</t>
+          <t>745810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5060</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>11952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30467</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401639</t>
+          <t>401196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415750</t>
+          <t>414839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318564</t>
+          <t>317931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332951</t>
+          <t>332341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726341</t>
+          <t>726357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745644</t>
+          <t>744856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18156</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>41940</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32410</t>
+          <t>32904</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35747</t>
+          <t>37047</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63944</t>
+          <t>65268</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>587978</t>
+          <t>586424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610208</t>
+          <t>610080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226715</t>
+          <t>226221</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245000</t>
+          <t>244491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>823545</t>
+          <t>822221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>851742</t>
+          <t>850442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68445</t>
+          <t>67440</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69782</t>
+          <t>68501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106910</t>
+          <t>105376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1109659</t>
+          <t>1111783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135081</t>
+          <t>1134561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>690183</t>
+          <t>691188</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720600</t>
+          <t>719648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1809629</t>
+          <t>1811163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1846757</t>
+          <t>1848038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67669</t>
+          <t>69260</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103501</t>
+          <t>103729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114758</t>
+          <t>116254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>494828</t>
+          <t>494636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506640</t>
+          <t>506613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655708</t>
+          <t>655480</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>691540</t>
+          <t>689949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1155048</t>
+          <t>1153552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1193047</t>
+          <t>1192089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88598</t>
+          <t>88309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>130311</t>
+          <t>129446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>87132</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126906</t>
+          <t>126729</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>979040</t>
+          <t>979905</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1020753</t>
+          <t>1021042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1249327</t>
+          <t>1249504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1287104</t>
+          <t>1289101</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65449</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103381</t>
+          <t>105020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>249840</t>
+          <t>252255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>319036</t>
+          <t>317264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>330664</t>
+          <t>332013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>408253</t>
+          <t>407616</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3316380</t>
+          <t>3314741</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3354312</t>
+          <t>3354570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3219743</t>
+          <t>3221515</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3288939</t>
+          <t>3286524</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6550287</t>
+          <t>6550924</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6627876</t>
+          <t>6626527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2016</t>
+          <t>Población cuya depresión o ansiedad le limita en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9547</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>18424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>23972</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>419545</t>
+          <t>420066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428085</t>
+          <t>428086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328127</t>
+          <t>328631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>342411</t>
+          <t>342099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752591</t>
+          <t>752175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768283</t>
+          <t>768131</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366201</t>
+          <t>365345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375389</t>
+          <t>375376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353815</t>
+          <t>355618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368161</t>
+          <t>368490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727330</t>
+          <t>727036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>742010</t>
+          <t>741702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14618</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34263</t>
+          <t>35274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507296</t>
+          <t>507556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519006</t>
+          <t>519104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142112</t>
+          <t>141690</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157519</t>
+          <t>157531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653773</t>
+          <t>652762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673836</t>
+          <t>673828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43554</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>29158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55805</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89628</t>
+          <t>90353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106084</t>
+          <t>1106561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1129162</t>
+          <t>1129065</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>770071</t>
+          <t>771208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>796736</t>
+          <t>796718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885886</t>
+          <t>1885161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1920162</t>
+          <t>1919975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56698</t>
+          <t>54750</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89375</t>
+          <t>90089</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72937</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111580</t>
+          <t>111760</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>591801</t>
+          <t>591442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609184</t>
+          <t>608806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648869</t>
+          <t>648155</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>681546</t>
+          <t>683494</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1247370</t>
+          <t>1247190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1286013</t>
+          <t>1284825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>73400</t>
+          <t>72987</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111512</t>
+          <t>110072</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>74098</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114174</t>
+          <t>112033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281529</t>
+          <t>282357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>970513</t>
+          <t>971953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1008625</t>
+          <t>1009038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1254996</t>
+          <t>1257137</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1293406</t>
+          <t>1295072</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>51052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86095</t>
+          <t>83777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>208471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>269968</t>
+          <t>269509</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269837</t>
+          <t>269109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339632</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3299627</t>
+          <t>3301945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3334017</t>
+          <t>3334670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3261628</t>
+          <t>3262087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3325796</t>
+          <t>3323125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6577686</t>
+          <t>6574738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6647481</t>
+          <t>6648209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya depresión o ansiedad le limita en 2023</t>
+          <t>Población cuya depresión o ansiedad le limita en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32137</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>23966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45542</t>
+          <t>44262</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484530</t>
+          <t>486064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499944</t>
+          <t>499922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415330</t>
+          <t>415206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>431738</t>
+          <t>431703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>907137</t>
+          <t>908417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928596</t>
+          <t>928713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29034</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51380</t>
+          <t>49924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432458</t>
+          <t>432126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445653</t>
+          <t>445504</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346904</t>
+          <t>346754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363697</t>
+          <t>363557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783413</t>
+          <t>784869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>805759</t>
+          <t>805972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40357</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23970</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>60373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>627907</t>
+          <t>626655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661448</t>
+          <t>661145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142941</t>
+          <t>143215</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155290</t>
+          <t>154861</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>772694</t>
+          <t>774802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>819811</t>
+          <t>818214</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34142</t>
+          <t>32723</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60380</t>
+          <t>59078</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27978</t>
+          <t>31177</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79165</t>
+          <t>79529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74929</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123537</t>
+          <t>123909</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>974439</t>
+          <t>975741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1000677</t>
+          <t>1002096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898929</t>
+          <t>898565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950116</t>
+          <t>946917</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889375</t>
+          <t>1889003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937983</t>
+          <t>1942881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>33542</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55823</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92324</t>
+          <t>93809</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79661</t>
+          <t>78428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118280</t>
+          <t>119745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>442219</t>
+          <t>441504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>460072</t>
+          <t>460364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>749011</t>
+          <t>747526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>785512</t>
+          <t>784160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1198101</t>
+          <t>1196636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1236720</t>
+          <t>1237953</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49931</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>75946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58105</t>
+          <t>57523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87526</t>
+          <t>91289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215908</t>
+          <t>215818</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236068</t>
+          <t>235847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>683913</t>
+          <t>685425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>712154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>914352</t>
+          <t>910589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>943773</t>
+          <t>944355</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91873</t>
+          <t>94247</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>150067</t>
+          <t>148869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>211026</t>
+          <t>214278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291492</t>
+          <t>294195</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327582</t>
+          <t>329709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426011</t>
+          <t>426236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3225993</t>
+          <t>3227191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3284187</t>
+          <t>3281813</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3286266</t>
+          <t>3283563</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3366732</t>
+          <t>3363480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6527807</t>
+          <t>6527582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6626236</t>
+          <t>6624109</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P14B23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P14B23-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424233</t>
+          <t>421742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435285</t>
+          <t>435224</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298639</t>
+          <t>298504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>312588</t>
+          <t>312554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727981</t>
+          <t>728272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745810</t>
+          <t>745188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17601</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20080</t>
+          <t>18999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>31393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401196</t>
+          <t>402446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414839</t>
+          <t>415711</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>317931</t>
+          <t>319012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332341</t>
+          <t>332899</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>726357</t>
+          <t>725415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744856</t>
+          <t>745009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>39310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37047</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>64401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>586424</t>
+          <t>589054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>610080</t>
+          <t>610759</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226221</t>
+          <t>226190</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244491</t>
+          <t>244834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>822221</t>
+          <t>823088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>850442</t>
+          <t>850540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46128</t>
+          <t>48773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38980</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67440</t>
+          <t>67055</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68501</t>
+          <t>68408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105376</t>
+          <t>105732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1111783</t>
+          <t>1109138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1134561</t>
+          <t>1135176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>691188</t>
+          <t>691573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719648</t>
+          <t>720079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1811163</t>
+          <t>1810807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1848038</t>
+          <t>1848131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69260</t>
+          <t>69652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103729</t>
+          <t>103534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77717</t>
+          <t>76743</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116254</t>
+          <t>113673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>494636</t>
+          <t>494259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506613</t>
+          <t>506604</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655480</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>689949</t>
+          <t>689557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1153552</t>
+          <t>1156133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1192089</t>
+          <t>1193063</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88309</t>
+          <t>90119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>129446</t>
+          <t>130813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>88582</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126729</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>979905</t>
+          <t>978538</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1021042</t>
+          <t>1019232</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1249504</t>
+          <t>1249849</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1289101</t>
+          <t>1287651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65191</t>
+          <t>66091</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>103406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252255</t>
+          <t>255810</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>317264</t>
+          <t>320709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332013</t>
+          <t>335673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407616</t>
+          <t>409515</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3314741</t>
+          <t>3316355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3354570</t>
+          <t>3353670</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3221515</t>
+          <t>3218070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3286524</t>
+          <t>3282969</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6550924</t>
+          <t>6549025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6626527</t>
+          <t>6622867</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18424</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23972</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420066</t>
+          <t>420005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>428086</t>
+          <t>428095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328631</t>
+          <t>328434</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>342099</t>
+          <t>342236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752175</t>
+          <t>753015</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768131</t>
+          <t>768297</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365345</t>
+          <t>366616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375376</t>
+          <t>375388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355618</t>
+          <t>356483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368490</t>
+          <t>368518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727036</t>
+          <t>725421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>741702</t>
+          <t>741735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8592</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24433</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35274</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507556</t>
+          <t>507718</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519104</t>
+          <t>519063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141690</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157531</t>
+          <t>157199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652762</t>
+          <t>653533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673828</t>
+          <t>673644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29158</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55539</t>
+          <t>56005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90353</t>
+          <t>91363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106561</t>
+          <t>1106527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1129065</t>
+          <t>1129153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>771208</t>
+          <t>770141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>796718</t>
+          <t>795238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885161</t>
+          <t>1884151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1919975</t>
+          <t>1919509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29264</t>
+          <t>29428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>55527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90089</t>
+          <t>89366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>72375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111760</t>
+          <t>110830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>591442</t>
+          <t>591278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608806</t>
+          <t>608613</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648155</t>
+          <t>648878</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>683494</t>
+          <t>682717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1247190</t>
+          <t>1248120</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1284825</t>
+          <t>1286575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72987</t>
+          <t>74463</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110072</t>
+          <t>110849</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74098</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112033</t>
+          <t>112852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282357</t>
+          <t>283100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>971953</t>
+          <t>971176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1009038</t>
+          <t>1007562</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1257137</t>
+          <t>1256318</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1295072</t>
+          <t>1294337</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>52196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83777</t>
+          <t>84204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>208471</t>
+          <t>204552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>269509</t>
+          <t>267901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269109</t>
+          <t>272231</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>343325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3301945</t>
+          <t>3301518</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3334670</t>
+          <t>3333526</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3262087</t>
+          <t>3263695</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3323125</t>
+          <t>3327044</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6574738</t>
+          <t>6573993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6648209</t>
+          <t>6645087</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10334</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22849</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>36752</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>494878</t>
+          <t>539728</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>486064</t>
+          <t>530769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>499922</t>
+          <t>545123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>424618</t>
+          <t>462549</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415206</t>
+          <t>452194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>431703</t>
+          <t>469812</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>919497</t>
+          <t>1002277</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>908417</t>
+          <t>989463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928713</t>
+          <t>1013255</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11709</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26555</t>
+          <t>29674</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19023</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28821</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49924</t>
+          <t>54019</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>440504</t>
+          <t>471066</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>432126</t>
+          <t>463041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445504</t>
+          <t>476916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>356025</t>
+          <t>393469</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346754</t>
+          <t>383944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363557</t>
+          <t>401398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>796529</t>
+          <t>864534</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784869</t>
+          <t>852336</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>805972</t>
+          <t>875244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>23260</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41609</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16994</t>
+          <t>19267</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>27007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>42527</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60373</t>
+          <t>55378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645567</t>
+          <t>448352</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>626655</t>
+          <t>437762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>661145</t>
+          <t>456777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>149917</t>
+          <t>168230</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143215</t>
+          <t>160490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154861</t>
+          <t>174447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>795484</t>
+          <t>616582</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>774802</t>
+          <t>603731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818214</t>
+          <t>627617</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>44719</t>
+          <t>50288</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32723</t>
+          <t>38347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59078</t>
+          <t>64923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>65755</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31177</t>
+          <t>53818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79529</t>
+          <t>80149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>102154</t>
+          <t>116043</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70031</t>
+          <t>98025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123909</t>
+          <t>136789</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>990100</t>
+          <t>1081555</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>975741</t>
+          <t>1066920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1002096</t>
+          <t>1093496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>920659</t>
+          <t>795456</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898565</t>
+          <t>781062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946917</t>
+          <t>807393</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1910758</t>
+          <t>1877011</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1889003</t>
+          <t>1856265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1942881</t>
+          <t>1895029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>24445</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33542</t>
+          <t>35528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>84651</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57175</t>
+          <t>71394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93809</t>
+          <t>98463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>99202</t>
+          <t>109096</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>78428</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119745</t>
+          <t>127807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>452360</t>
+          <t>543519</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>441504</t>
+          <t>532436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>460364</t>
+          <t>552205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>764819</t>
+          <t>746199</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>747526</t>
+          <t>732387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>784160</t>
+          <t>759456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1217179</t>
+          <t>1289718</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1196636</t>
+          <t>1271007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1237953</t>
+          <t>1305145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61305</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49217</t>
+          <t>55164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75946</t>
+          <t>82949</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>71990</t>
+          <t>77602</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57523</t>
+          <t>62581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91289</t>
+          <t>97825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>229822</t>
+          <t>226622</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>215818</t>
+          <t>213705</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235847</t>
+          <t>232712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>700066</t>
+          <t>777285</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>685425</t>
+          <t>761332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>712154</t>
+          <t>789117</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>929888</t>
+          <t>1003907</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>910589</t>
+          <t>983684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>944355</t>
+          <t>1018928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>122829</t>
+          <t>131635</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94247</t>
+          <t>109553</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148869</t>
+          <t>157414</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,67 +8090,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>261653</t>
+          <t>292206</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>214278</t>
+          <t>266719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>294195</t>
+          <t>323507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>423841</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>388502</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>459234</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>384482</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>329709</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>426236</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3253231</t>
+          <t>3310841</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3227191</t>
+          <t>3285062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3281813</t>
+          <t>3332923</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,67 +8203,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3316105</t>
+          <t>3343187</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3283563</t>
+          <t>3311886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3363480</t>
+          <t>3368674</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7966</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6654028</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6618635</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6689367</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>94,01%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>7966</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6569336</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6527582</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6624109</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>94,47%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
